--- a/data/trans_orig/P6607-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>51592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78685</t>
+          <t>77229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75733</t>
+          <t>76051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99309</t>
+          <t>99688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134352</t>
+          <t>134790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171139</t>
+          <t>171817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24574</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>48139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46699</t>
+          <t>45899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>75216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>28246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35403</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>58941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59129</t>
+          <t>60505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>51156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80520</t>
+          <t>80832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311806</t>
+          <t>311190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>373163</t>
+          <t>371877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404444</t>
+          <t>405260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>448003</t>
+          <t>448646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>732710</t>
+          <t>732700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>811117</t>
+          <t>810195</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160380</t>
+          <t>158399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209177</t>
+          <t>210636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>97687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235386</t>
+          <t>230789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297755</t>
+          <t>294855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149369</t>
+          <t>150934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197027</t>
+          <t>201443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179449</t>
+          <t>182483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236234</t>
+          <t>234451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182103</t>
+          <t>184138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235535</t>
+          <t>235497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44223</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>211667</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269156</t>
+          <t>273069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147820</t>
+          <t>149288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185617</t>
+          <t>185790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156422</t>
+          <t>158691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185337</t>
+          <t>185270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>312981</t>
+          <t>315952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364176</t>
+          <t>363472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61944</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93957</t>
+          <t>94452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35772</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62619</t>
+          <t>61035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>105395</t>
+          <t>105188</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147538</t>
+          <t>147045</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>67344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>36349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>538702</t>
+          <t>538376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>613959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>661498</t>
+          <t>661091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>717326</t>
+          <t>717751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1215190</t>
+          <t>1213517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1313802</t>
+          <t>1314179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264810</t>
+          <t>268571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332162</t>
+          <t>329483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130003</t>
+          <t>128413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177155</t>
+          <t>175687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>412474</t>
+          <t>411752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487836</t>
+          <t>491702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>230365</t>
+          <t>230401</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>290502</t>
+          <t>289501</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66497</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>276972</t>
+          <t>275785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>346192</t>
+          <t>347269</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243422</t>
+          <t>245781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>304698</t>
+          <t>308339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68535</t>
+          <t>71047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>295304</t>
+          <t>293098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369578</t>
+          <t>363878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>49602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>60301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89232</t>
+          <t>88482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>36867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55360</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38306</t>
+          <t>38782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>61366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>48347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>75095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>280770</t>
+          <t>283160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>339936</t>
+          <t>341046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>419009</t>
+          <t>419400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>465310</t>
+          <t>466235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>710105</t>
+          <t>712535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>794422</t>
+          <t>794286</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214515</t>
+          <t>211919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267224</t>
+          <t>268689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108426</t>
+          <t>103465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148570</t>
+          <t>146055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330323</t>
+          <t>329213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403415</t>
+          <t>399359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142224</t>
+          <t>143950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191410</t>
+          <t>192551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57835</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182120</t>
+          <t>182316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239331</t>
+          <t>236205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179489</t>
+          <t>180384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>234362</t>
+          <t>230772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54330</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>219550</t>
+          <t>217710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279973</t>
+          <t>277790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181228</t>
+          <t>181993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218659</t>
+          <t>221161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218034</t>
+          <t>218390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248425</t>
+          <t>246995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410618</t>
+          <t>410362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>461968</t>
+          <t>458733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79887</t>
+          <t>77828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113630</t>
+          <t>112859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124818</t>
+          <t>124666</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>169011</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>45264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63664</t>
+          <t>63466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31248</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>507684</t>
+          <t>505799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>582650</t>
+          <t>580659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>683869</t>
+          <t>687754</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>745739</t>
+          <t>746341</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1206317</t>
+          <t>1209698</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1309625</t>
+          <t>1312147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328236</t>
+          <t>329735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>393174</t>
+          <t>394659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166531</t>
+          <t>167046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218651</t>
+          <t>219709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512076</t>
+          <t>514058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596918</t>
+          <t>596896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>202040</t>
+          <t>199406</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255663</t>
+          <t>255451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48937</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80227</t>
+          <t>80168</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>259909</t>
+          <t>259998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>325589</t>
+          <t>325812</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247859</t>
+          <t>248336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310019</t>
+          <t>307143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44834</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75895</t>
+          <t>75204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302146</t>
+          <t>302490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374614</t>
+          <t>370650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>51160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73033</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265807</t>
+          <t>268675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>206174</t>
+          <t>213723</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300816</t>
+          <t>301413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>259642</t>
+          <t>232322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>576374</t>
+          <t>575219</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>238090</t>
+          <t>240286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>70732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190139</t>
+          <t>174354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139167</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353650</t>
+          <t>356419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44646</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>152547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173041</t>
+          <t>173551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>167131</t>
+          <t>165864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>614043</t>
+          <t>625235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>48311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>184772</t>
+          <t>185840</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>746295</t>
+          <t>808960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152048</t>
+          <t>153741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183478</t>
+          <t>184145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163812</t>
+          <t>163441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179862</t>
+          <t>179352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322187</t>
+          <t>321248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358893</t>
+          <t>359022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>26111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>49156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70923</t>
+          <t>71608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>35938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25164</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>189417</t>
+          <t>198682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>484582</t>
+          <t>484624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>393808</t>
+          <t>365120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>498104</t>
+          <t>498252</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>538427</t>
+          <t>548929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>982367</t>
+          <t>985105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114107</t>
+          <t>118132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278733</t>
+          <t>277090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104829</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225167</t>
+          <t>245332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>216204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>440835</t>
+          <t>433384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65358</t>
+          <t>72858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178972</t>
+          <t>182524</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109783</t>
+          <t>104025</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>207928</t>
+          <t>206705</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193897</t>
+          <t>192862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>737602</t>
+          <t>703664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221699</t>
+          <t>222683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911758</t>
+          <t>933747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6607-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77229</t>
+          <t>78029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>74906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99688</t>
+          <t>98921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134790</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171817</t>
+          <t>172519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45899</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75216</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50552</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60505</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51156</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80832</t>
+          <t>80353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311190</t>
+          <t>313679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>371877</t>
+          <t>375856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>405260</t>
+          <t>406544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>448646</t>
+          <t>449790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>732700</t>
+          <t>735712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>810195</t>
+          <t>813274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158399</t>
+          <t>163582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210636</t>
+          <t>212371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97687</t>
+          <t>95675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230789</t>
+          <t>236931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294855</t>
+          <t>294183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150934</t>
+          <t>150273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201443</t>
+          <t>196779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>48520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182483</t>
+          <t>180474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234451</t>
+          <t>235740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184138</t>
+          <t>182297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235497</t>
+          <t>235314</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44179</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210537</t>
+          <t>212098</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>273069</t>
+          <t>270173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149288</t>
+          <t>148898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185790</t>
+          <t>186182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158691</t>
+          <t>157096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185270</t>
+          <t>185008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315952</t>
+          <t>318044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>363472</t>
+          <t>364004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62807</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94452</t>
+          <t>93287</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35449</t>
+          <t>36004</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61035</t>
+          <t>62389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>105188</t>
+          <t>103644</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147045</t>
+          <t>146824</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37696</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67344</t>
+          <t>66277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>75212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30843</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>538376</t>
+          <t>535834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>613959</t>
+          <t>613367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>661091</t>
+          <t>662401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>717751</t>
+          <t>717025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1213517</t>
+          <t>1215149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1314179</t>
+          <t>1318604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268571</t>
+          <t>267949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329483</t>
+          <t>332455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,82 +2567,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>151411</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>132157</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>176769</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>448945</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>408670</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>490447</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>19,07%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>151411</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>128413</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>175687</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>448945</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>411752</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>491702</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>230401</t>
+          <t>230168</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>289501</t>
+          <t>289757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>67442</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>275785</t>
+          <t>279404</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>347269</t>
+          <t>349178</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>245781</t>
+          <t>243664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>308339</t>
+          <t>304863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293098</t>
+          <t>295929</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>363878</t>
+          <t>367447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49602</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60301</t>
+          <t>60090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88482</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36867</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55014</t>
+          <t>53543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37991</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>38899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61366</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75095</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283160</t>
+          <t>282558</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>341046</t>
+          <t>341265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>419400</t>
+          <t>416741</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>466235</t>
+          <t>465349</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>712535</t>
+          <t>711242</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>794286</t>
+          <t>791656</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211919</t>
+          <t>214022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268689</t>
+          <t>268413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103465</t>
+          <t>107154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146055</t>
+          <t>148778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329213</t>
+          <t>331330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399359</t>
+          <t>401462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143950</t>
+          <t>144582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192551</t>
+          <t>196352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>56655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182316</t>
+          <t>181311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236205</t>
+          <t>236219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180384</t>
+          <t>178303</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>230772</t>
+          <t>230903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54849</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>217710</t>
+          <t>220468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>277790</t>
+          <t>275533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181993</t>
+          <t>182466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221161</t>
+          <t>221524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218390</t>
+          <t>218264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246995</t>
+          <t>248817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410362</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458733</t>
+          <t>458948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77828</t>
+          <t>77841</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112859</t>
+          <t>112499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124666</t>
+          <t>123911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>170487</t>
+          <t>166779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45264</t>
+          <t>44583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63466</t>
+          <t>63857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4771,42 +4771,42 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>26941</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>17585</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>38557</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>26941</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>39066</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>505799</t>
+          <t>506089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>580659</t>
+          <t>584134</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>687754</t>
+          <t>687576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>746341</t>
+          <t>747767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1209698</t>
+          <t>1214373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1312147</t>
+          <t>1313472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>329735</t>
+          <t>329965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394659</t>
+          <t>395145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167046</t>
+          <t>167018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219709</t>
+          <t>216905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514058</t>
+          <t>514064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596896</t>
+          <t>592054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199406</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>255451</t>
+          <t>257618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>259998</t>
+          <t>260057</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>325812</t>
+          <t>325556</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>248336</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307143</t>
+          <t>308947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>73462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302490</t>
+          <t>300037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370650</t>
+          <t>367666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5741,32 +5741,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,32 +5776,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,32 +5811,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51160</t>
+          <t>56621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -5854,17 +5854,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,32 +5889,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,32 +5924,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26697</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>46487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -5967,32 +5967,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16043</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,32 +6002,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,32 +6037,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -6080,32 +6080,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>48153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,32 +6115,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,32 +6150,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -6193,17 +6193,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,17 +6228,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6310,32 +6310,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>177517</t>
+          <t>192208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65990</t>
+          <t>169251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>268675</t>
+          <t>219338</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6345,32 +6345,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>272001</t>
+          <t>302071</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>213723</t>
+          <t>281686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>301413</t>
+          <t>319681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6380,32 +6380,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>449518</t>
+          <t>494280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>232322</t>
+          <t>459507</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>575219</t>
+          <t>528328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>158631</t>
+          <t>167542</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>142182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240286</t>
+          <t>191308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>77458</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>63067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174354</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,32 +6493,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>262785</t>
+          <t>244999</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141038</t>
+          <t>216931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356419</t>
+          <t>275477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -6536,32 +6536,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>116069</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>96878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152547</t>
+          <t>141316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,32 +6571,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>130641</t>
+          <t>148396</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67403</t>
+          <t>124433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173551</t>
+          <t>171642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -6649,32 +6649,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>367345</t>
+          <t>145160</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165864</t>
+          <t>121237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>625235</t>
+          <t>170851</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,32 +6684,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36827</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>32526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,32 +6719,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>404173</t>
+          <t>188023</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>185840</t>
+          <t>164099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>808960</t>
+          <t>217906</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -6762,17 +6762,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6879,32 +6879,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>169469</t>
+          <t>186405</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153741</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184145</t>
+          <t>202292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,32 +6914,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172693</t>
+          <t>188383</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163441</t>
+          <t>178479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179352</t>
+          <t>196763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>374788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321248</t>
+          <t>353160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359022</t>
+          <t>392783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -6992,32 +6992,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36583</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49156</t>
+          <t>57647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7027,32 +7027,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7062,32 +7062,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>57313</t>
+          <t>66920</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43947</t>
+          <t>53545</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71608</t>
+          <t>83940</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -7105,32 +7105,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38396</t>
+          <t>42395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,67 +7253,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>18749</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>11077</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>32056</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>16368</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>9233</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>29091</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>366644</t>
+          <t>398826</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>198682</t>
+          <t>362193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>484624</t>
+          <t>432472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>466154</t>
+          <t>515112</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>494051</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>498252</t>
+          <t>536914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,32 +7518,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>832798</t>
+          <t>913937</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>548929</t>
+          <t>871674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>985105</t>
+          <t>959411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>209866</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>202801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277090</t>
+          <t>263254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7596,32 +7596,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>136929</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101706</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245332</t>
+          <t>134205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>346795</t>
+          <t>347159</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>311145</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433384</t>
+          <t>383618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -7674,32 +7674,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>151420</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72858</t>
+          <t>128403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182524</t>
+          <t>177818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7709,32 +7709,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7744,32 +7744,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>166728</t>
+          <t>189560</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>161315</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>220013</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7787,32 +7787,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>403284</t>
+          <t>196675</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192862</t>
+          <t>170193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>703664</t>
+          <t>227002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,32 +7822,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>446457</t>
+          <t>246787</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>222683</t>
+          <t>217616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>933747</t>
+          <t>283721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -7900,17 +7900,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
